--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-07-2025.xlsx
@@ -2421,12 +2421,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationuk.co.uk', port=443): Max retries exceeded with url: /products/625mm-celotex-pl4050-pir-insulated-plasterboard-2400mm-x-1200mm-625mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000022BCBD8B050&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>£40.21</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Max retries exceeded with url: /625mm-celotex-pl4050-pir-insulated-plasterboard---12m-x-24m-610-p.asp (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000022BCBD8B610&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>£39.41</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£58.00</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
